--- a/artfynd/A 1095-2026 artfynd.xlsx
+++ b/artfynd/A 1095-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>132695652</v>
       </c>
       <c r="B2" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>132695598</v>
       </c>
       <c r="B3" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>132695329</v>
       </c>
       <c r="B4" t="n">
-        <v>92364</v>
+        <v>92368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>132695395</v>
       </c>
       <c r="B5" t="n">
-        <v>79323</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>132695489</v>
       </c>
       <c r="B6" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132695568</v>
+        <v>132695613</v>
       </c>
       <c r="B7" t="n">
-        <v>57949</v>
+        <v>91908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1217,31 +1217,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1249,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>758180</v>
+        <v>758175</v>
       </c>
       <c r="R7" t="n">
-        <v>7176196</v>
+        <v>7176287</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,17 +1282,13 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1316,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132695613</v>
+        <v>132695568</v>
       </c>
       <c r="B8" t="n">
-        <v>91904</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,26 +1318,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1354,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>758175</v>
+        <v>758180</v>
       </c>
       <c r="R8" t="n">
-        <v>7176287</v>
+        <v>7176196</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1392,13 +1388,17 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>132695423</v>
       </c>
       <c r="B9" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1524,6 +1524,2285 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132710617</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79359</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>185</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>758191</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7176257</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132710436</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91908</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>758168</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7176186</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132710910</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>757931</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7176106</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ovanligt riklig förekomst, många draperade träd!</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132710187</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>758157</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7176228</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>påbörjade bohål i gran, 1,5-2 meters höjd, ca 4 cm i diameter, även barksprätt på samma gran</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132710895</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>757927</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7176110</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132710791</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>757951</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7176128</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>fertil garnlav, mycket riklig garnlavsförekomst</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132710803</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92368</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>757951</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7176128</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren, Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132710636</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>758195</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7176255</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>fertil garnlav, ovanligt rikligt med apothecier!</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132710963</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>757893</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7176108</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132710416</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91908</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>758184</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7176186</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132710603</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>758186</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7176281</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>påbörjat bohål ca 2 meter upp i granstam</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132710466</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99116</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>758166</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7176297</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren, Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132710491</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>758179</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7176301</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132710116</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>758131</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7176202</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132710050</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>757934</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7176139</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>mycket rik förekomst med många draperade träd!</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132710403</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91908</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>758173</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7176192</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132710098</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>758128</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7176201</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132710308</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>758164</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7176213</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>hane observerad på nära håll, födosökande på en gran, sprättade bort bark</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Patrik Nygren, Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132710580</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>758189</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7176283</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132710822</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>757927</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7176110</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>hål hackade i gran</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132710780</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stortjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>758184</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7176243</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1095-2026 artfynd.xlsx
+++ b/artfynd/A 1095-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132695652</v>
+        <v>132695598</v>
       </c>
       <c r="B2" t="n">
         <v>57953</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758192</v>
+        <v>758145</v>
       </c>
       <c r="R2" t="n">
-        <v>7176243</v>
+        <v>7176182</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132695598</v>
+        <v>132695652</v>
       </c>
       <c r="B3" t="n">
         <v>57953</v>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758145</v>
+        <v>758192</v>
       </c>
       <c r="R3" t="n">
-        <v>7176182</v>
+        <v>7176243</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -895,32 +895,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132695329</v>
+        <v>132695395</v>
       </c>
       <c r="B4" t="n">
-        <v>92368</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>757943</v>
+        <v>757961</v>
       </c>
       <c r="R4" t="n">
-        <v>7176149</v>
+        <v>7176156</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132695395</v>
+        <v>132695329</v>
       </c>
       <c r="B5" t="n">
-        <v>79327</v>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>757961</v>
+        <v>757943</v>
       </c>
       <c r="R5" t="n">
-        <v>7176156</v>
+        <v>7176149</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1209,7 +1209,7 @@
         <v>132695613</v>
       </c>
       <c r="B7" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>132710436</v>
       </c>
       <c r="B11" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>132710803</v>
       </c>
       <c r="B16" t="n">
-        <v>92368</v>
+        <v>92369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>132710416</v>
       </c>
       <c r="B19" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>132710466</v>
       </c>
       <c r="B21" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>132710403</v>
       </c>
       <c r="B25" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3586,10 +3586,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132710822</v>
+        <v>132710780</v>
       </c>
       <c r="B29" t="n">
-        <v>57950</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3597,16 +3597,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>757927</v>
+        <v>758184</v>
       </c>
       <c r="R29" t="n">
-        <v>7176110</v>
+        <v>7176243</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3669,14 +3669,14 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>hål hackade i gran</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG29" t="b">
         <v>0</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132710780</v>
+        <v>132710822</v>
       </c>
       <c r="B30" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3707,16 +3707,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>758184</v>
+        <v>757927</v>
       </c>
       <c r="R30" t="n">
-        <v>7176243</v>
+        <v>7176110</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3779,14 +3779,14 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hål hackade i gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="b">
         <v>0</v>

--- a/artfynd/A 1095-2026 artfynd.xlsx
+++ b/artfynd/A 1095-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132695598</v>
+        <v>132695652</v>
       </c>
       <c r="B2" t="n">
         <v>57953</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758145</v>
+        <v>758192</v>
       </c>
       <c r="R2" t="n">
-        <v>7176182</v>
+        <v>7176243</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132695652</v>
+        <v>132695598</v>
       </c>
       <c r="B3" t="n">
         <v>57953</v>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758192</v>
+        <v>758145</v>
       </c>
       <c r="R3" t="n">
-        <v>7176243</v>
+        <v>7176182</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132695613</v>
+        <v>132695568</v>
       </c>
       <c r="B7" t="n">
-        <v>91909</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1217,26 +1217,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1244,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>758175</v>
+        <v>758180</v>
       </c>
       <c r="R7" t="n">
-        <v>7176287</v>
+        <v>7176196</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1282,13 +1287,17 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1307,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132695568</v>
+        <v>132695613</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,31 +1327,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1350,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>758180</v>
+        <v>758175</v>
       </c>
       <c r="R8" t="n">
-        <v>7176196</v>
+        <v>7176287</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1388,17 +1392,13 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -2610,42 +2610,42 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132710603</v>
+        <v>132710466</v>
       </c>
       <c r="B20" t="n">
-        <v>57953</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>758186</v>
+        <v>758166</v>
       </c>
       <c r="R20" t="n">
-        <v>7176281</v>
+        <v>7176297</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2691,17 +2691,13 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>påbörjat bohål ca 2 meter upp i granstam</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2713,49 +2709,49 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström, Patrik Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132710466</v>
+        <v>132710603</v>
       </c>
       <c r="B21" t="n">
-        <v>99117</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2763,10 +2759,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>758166</v>
+        <v>758186</v>
       </c>
       <c r="R21" t="n">
-        <v>7176297</v>
+        <v>7176281</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2801,13 +2797,17 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>påbörjat bohål ca 2 meter upp i granstam</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3476,10 +3476,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132710580</v>
+        <v>132710822</v>
       </c>
       <c r="B28" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3487,16 +3487,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3519,10 +3519,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>758189</v>
+        <v>757927</v>
       </c>
       <c r="R28" t="n">
-        <v>7176283</v>
+        <v>7176110</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3559,14 +3559,14 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hål hackade i gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="b">
         <v>0</v>
@@ -3586,7 +3586,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132710780</v>
+        <v>132710580</v>
       </c>
       <c r="B29" t="n">
         <v>57953</v>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>758184</v>
+        <v>758189</v>
       </c>
       <c r="R29" t="n">
-        <v>7176243</v>
+        <v>7176283</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132710822</v>
+        <v>132710780</v>
       </c>
       <c r="B30" t="n">
-        <v>57950</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3707,16 +3707,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>757927</v>
+        <v>758184</v>
       </c>
       <c r="R30" t="n">
-        <v>7176110</v>
+        <v>7176243</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3779,14 +3779,14 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>hål hackade i gran</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG30" t="b">
         <v>0</v>

--- a/artfynd/A 1095-2026 artfynd.xlsx
+++ b/artfynd/A 1095-2026 artfynd.xlsx
@@ -895,32 +895,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132695329</v>
+        <v>132695395</v>
       </c>
       <c r="B4" t="n">
-        <v>92378</v>
+        <v>79333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>757943</v>
+        <v>757961</v>
       </c>
       <c r="R4" t="n">
-        <v>7176149</v>
+        <v>7176156</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132695395</v>
+        <v>132695329</v>
       </c>
       <c r="B5" t="n">
-        <v>79333</v>
+        <v>92378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1034,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>757961</v>
+        <v>757943</v>
       </c>
       <c r="R5" t="n">
-        <v>7176156</v>
+        <v>7176149</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132695568</v>
+        <v>132695613</v>
       </c>
       <c r="B7" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1217,31 +1217,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1249,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>758180</v>
+        <v>758175</v>
       </c>
       <c r="R7" t="n">
-        <v>7176196</v>
+        <v>7176287</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,17 +1282,13 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1316,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132695613</v>
+        <v>132695568</v>
       </c>
       <c r="B8" t="n">
-        <v>91918</v>
+        <v>57958</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,26 +1318,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1354,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>758175</v>
+        <v>758180</v>
       </c>
       <c r="R8" t="n">
-        <v>7176287</v>
+        <v>7176196</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1392,13 +1388,17 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -3476,10 +3476,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132710822</v>
+        <v>132710580</v>
       </c>
       <c r="B28" t="n">
-        <v>57955</v>
+        <v>57958</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3487,16 +3487,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3519,10 +3519,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>757927</v>
+        <v>758189</v>
       </c>
       <c r="R28" t="n">
-        <v>7176110</v>
+        <v>7176283</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3559,14 +3559,14 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>hål hackade i gran</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG28" t="b">
         <v>0</v>
@@ -3586,7 +3586,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132710580</v>
+        <v>132710780</v>
       </c>
       <c r="B29" t="n">
         <v>57958</v>
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>758189</v>
+        <v>758184</v>
       </c>
       <c r="R29" t="n">
-        <v>7176283</v>
+        <v>7176243</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132710780</v>
+        <v>132710822</v>
       </c>
       <c r="B30" t="n">
-        <v>57958</v>
+        <v>57955</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3707,16 +3707,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>758184</v>
+        <v>757927</v>
       </c>
       <c r="R30" t="n">
-        <v>7176243</v>
+        <v>7176110</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3779,14 +3779,14 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>hål hackade i gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="b">
         <v>0</v>

--- a/artfynd/A 1095-2026 artfynd.xlsx
+++ b/artfynd/A 1095-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132695652</v>
+        <v>132710617</v>
       </c>
       <c r="B2" t="n">
-        <v>57958</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,45 +686,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mörttjärnliden, Vb</t>
+          <t>Stortjärnliden, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758192</v>
+        <v>758191</v>
       </c>
       <c r="R2" t="n">
-        <v>7176243</v>
+        <v>7176257</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,39 +755,35 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132695598</v>
+        <v>132695613</v>
       </c>
       <c r="B3" t="n">
-        <v>57958</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,31 +791,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758145</v>
+        <v>758175</v>
       </c>
       <c r="R3" t="n">
-        <v>7176182</v>
+        <v>7176287</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,17 +856,13 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,10 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132695395</v>
+        <v>132710403</v>
       </c>
       <c r="B4" t="n">
-        <v>79333</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,40 +892,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mörttjärnliden, Vb</t>
+          <t>Stortjärnliden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>757961</v>
+        <v>758173</v>
       </c>
       <c r="R4" t="n">
-        <v>7176156</v>
+        <v>7176192</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,63 +974,67 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132695329</v>
+        <v>132710416</v>
       </c>
       <c r="B5" t="n">
-        <v>92378</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mörttjärnliden, Vb</t>
+          <t>Stortjärnliden, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>757943</v>
+        <v>758184</v>
       </c>
       <c r="R5" t="n">
-        <v>7176149</v>
+        <v>7176186</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,22 +1079,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132695489</v>
+        <v>132710436</v>
       </c>
       <c r="B6" t="n">
-        <v>57958</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,49 +1102,44 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mörttjärnliden, Vb</t>
+          <t>Stortjärnliden, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>758168</v>
       </c>
       <c r="R6" t="n">
-        <v>7176214</v>
+        <v>7176186</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,28 +1177,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132695568</v>
+        <v>132695329</v>
       </c>
       <c r="B7" t="n">
-        <v>57958</v>
+        <v>92406</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1217,31 +1207,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1249,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>758180</v>
+        <v>757943</v>
       </c>
       <c r="R7" t="n">
-        <v>7176196</v>
+        <v>7176149</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1287,17 +1272,13 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1316,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132695613</v>
+        <v>132710803</v>
       </c>
       <c r="B8" t="n">
-        <v>91918</v>
+        <v>92406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,40 +1308,44 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mörttjärnliden, Vb</t>
+          <t>Stortjärnliden, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>758175</v>
+        <v>757951</v>
       </c>
       <c r="R8" t="n">
-        <v>7176287</v>
+        <v>7176128</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1405,54 +1390,49 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren, Tommy Boström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132695423</v>
+        <v>132695395</v>
       </c>
       <c r="B9" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1460,10 +1440,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>758138</v>
+        <v>757961</v>
       </c>
       <c r="R9" t="n">
-        <v>7176215</v>
+        <v>7176156</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1498,17 +1478,13 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1527,32 +1503,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132710617</v>
+        <v>132710050</v>
       </c>
       <c r="B10" t="n">
-        <v>79365</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1569,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>758191</v>
+        <v>757934</v>
       </c>
       <c r="R10" t="n">
-        <v>7176257</v>
+        <v>7176139</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1605,6 +1581,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>mycket rik förekomst med många draperade träd!</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1632,38 +1613,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132710436</v>
+        <v>132710116</v>
       </c>
       <c r="B11" t="n">
-        <v>91918</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1674,10 +1655,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>758168</v>
+        <v>758131</v>
       </c>
       <c r="R11" t="n">
-        <v>7176186</v>
+        <v>7176202</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,14 +1718,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132710910</v>
+        <v>132710636</v>
       </c>
       <c r="B12" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1771,7 +1752,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1779,10 +1764,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>757931</v>
+        <v>758195</v>
       </c>
       <c r="R12" t="n">
-        <v>7176106</v>
+        <v>7176255</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1819,7 +1804,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ovanligt riklig förekomst, många draperade träd!</t>
+          <t>fertil garnlav, ovanligt rikligt med apothecier!</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,40 +1832,43 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132710187</v>
+        <v>132710791</v>
       </c>
       <c r="B13" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1890,10 +1878,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>758157</v>
+        <v>757951</v>
       </c>
       <c r="R13" t="n">
-        <v>7176228</v>
+        <v>7176128</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1930,7 +1918,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>påbörjade bohål i gran, 1,5-2 meters höjd, ca 4 cm i diameter, även barksprätt på samma gran</t>
+          <t>fertil garnlav, mycket riklig garnlavsförekomst</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,6 +1927,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1957,42 +1946,41 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132710895</v>
+        <v>132710910</v>
       </c>
       <c r="B14" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2000,10 +1988,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>757927</v>
+        <v>757931</v>
       </c>
       <c r="R14" t="n">
-        <v>7176110</v>
+        <v>7176106</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2040,15 +2028,16 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>barksprätt på gran</t>
+          <t>ovanligt riklig förekomst, många draperade träd!</t>
         </is>
       </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2067,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132710791</v>
+        <v>132710963</v>
       </c>
       <c r="B15" t="n">
-        <v>79333</v>
+        <v>80488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2078,21 +2067,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2101,11 +2090,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2113,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>757951</v>
+        <v>757893</v>
       </c>
       <c r="R15" t="n">
-        <v>7176128</v>
+        <v>7176108</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2149,11 +2134,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>fertil garnlav, mycket riklig garnlavsförekomst</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2181,41 +2161,42 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132710803</v>
+        <v>132710822</v>
       </c>
       <c r="B16" t="n">
-        <v>92378</v>
+        <v>57972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2223,10 +2204,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>757951</v>
+        <v>757927</v>
       </c>
       <c r="R16" t="n">
-        <v>7176128</v>
+        <v>7176110</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2261,13 +2242,17 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>hål hackade i gran</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2279,17 +2264,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132710636</v>
+        <v>132695423</v>
       </c>
       <c r="B17" t="n">
-        <v>79333</v>
+        <v>57975</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2297,48 +2282,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stortjärnliden, Vb</t>
+          <t>Mörttjärnliden, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>758195</v>
+        <v>758138</v>
       </c>
       <c r="R17" t="n">
-        <v>7176255</v>
+        <v>7176215</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2372,7 +2354,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>fertil garnlav, ovanligt rikligt med apothecier!</t>
+          <t>Barksprätt på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2381,29 +2363,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132710963</v>
+        <v>132695489</v>
       </c>
       <c r="B18" t="n">
-        <v>80438</v>
+        <v>57975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2411,44 +2392,49 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stortjärnliden, Vb</t>
+          <t>Mörttjärnliden, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>757893</v>
+        <v>758168</v>
       </c>
       <c r="R18" t="n">
-        <v>7176108</v>
+        <v>7176214</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2486,29 +2472,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132710416</v>
+        <v>132695568</v>
       </c>
       <c r="B19" t="n">
-        <v>91918</v>
+        <v>57975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2516,44 +2501,45 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stortjärnliden, Vb</t>
+          <t>Mörttjärnliden, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>758184</v>
+        <v>758180</v>
       </c>
       <c r="R19" t="n">
-        <v>7176186</v>
+        <v>7176196</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2585,35 +2571,39 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132710603</v>
+        <v>132695598</v>
       </c>
       <c r="B20" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2649,17 +2639,17 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stortjärnliden, Vb</t>
+          <t>Mörttjärnliden, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>758186</v>
+        <v>758145</v>
       </c>
       <c r="R20" t="n">
-        <v>7176281</v>
+        <v>7176182</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2693,7 +2683,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>påbörjat bohål ca 2 meter upp i granstam</t>
+          <t>Barksprätt på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2708,68 +2698,68 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132710466</v>
+        <v>132695652</v>
       </c>
       <c r="B21" t="n">
-        <v>99130</v>
+        <v>57975</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stortjärnliden, Vb</t>
+          <t>Mörttjärnliden, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>758166</v>
+        <v>758192</v>
       </c>
       <c r="R21" t="n">
-        <v>7176297</v>
+        <v>7176243</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2801,35 +2791,39 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Tommy Boström</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132710491</v>
+        <v>132710098</v>
       </c>
       <c r="B22" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2869,10 +2863,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>758179</v>
+        <v>758128</v>
       </c>
       <c r="R22" t="n">
-        <v>7176301</v>
+        <v>7176201</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2936,10 +2930,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132710116</v>
+        <v>132710187</v>
       </c>
       <c r="B23" t="n">
-        <v>79333</v>
+        <v>57975</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2947,30 +2941,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2978,10 +2973,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>758131</v>
+        <v>758157</v>
       </c>
       <c r="R23" t="n">
-        <v>7176202</v>
+        <v>7176228</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3016,13 +3011,17 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>påbörjade bohål i gran, 1,5-2 meters höjd, ca 4 cm i diameter, även barksprätt på samma gran</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3041,10 +3040,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132710050</v>
+        <v>132710308</v>
       </c>
       <c r="B24" t="n">
-        <v>79333</v>
+        <v>57975</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3052,30 +3051,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>757934</v>
+        <v>758164</v>
       </c>
       <c r="R24" t="n">
-        <v>7176139</v>
+        <v>7176213</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>mycket rik förekomst med många draperade träd!</t>
+          <t>hane observerad på nära håll, födosökande på en gran, sprättade bort bark</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3132,7 +3132,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3144,17 +3143,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Tommy Boström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132710403</v>
+        <v>132710491</v>
       </c>
       <c r="B25" t="n">
-        <v>91918</v>
+        <v>57975</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3162,30 +3161,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>758173</v>
+        <v>758179</v>
       </c>
       <c r="R25" t="n">
-        <v>7176192</v>
+        <v>7176301</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3231,13 +3231,17 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3256,10 +3260,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132710098</v>
+        <v>132710580</v>
       </c>
       <c r="B26" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3299,10 +3303,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>758128</v>
+        <v>758189</v>
       </c>
       <c r="R26" t="n">
-        <v>7176201</v>
+        <v>7176283</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3366,10 +3370,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132710308</v>
+        <v>132710603</v>
       </c>
       <c r="B27" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3399,7 +3403,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3409,10 +3413,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>758164</v>
+        <v>758186</v>
       </c>
       <c r="R27" t="n">
-        <v>7176213</v>
+        <v>7176281</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3449,7 +3453,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>hane observerad på nära håll, födosökande på en gran, sprättade bort bark</t>
+          <t>påbörjat bohål ca 2 meter upp i granstam</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3469,17 +3473,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132710822</v>
+        <v>132710780</v>
       </c>
       <c r="B28" t="n">
-        <v>57955</v>
+        <v>57975</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3487,16 +3491,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3519,10 +3523,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>757927</v>
+        <v>758184</v>
       </c>
       <c r="R28" t="n">
-        <v>7176110</v>
+        <v>7176243</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3559,14 +3563,14 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>hål hackade i gran</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG28" t="b">
         <v>0</v>
@@ -3586,10 +3590,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132710580</v>
+        <v>132710895</v>
       </c>
       <c r="B29" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3629,10 +3633,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>758189</v>
+        <v>757927</v>
       </c>
       <c r="R29" t="n">
-        <v>7176283</v>
+        <v>7176110</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3696,42 +3700,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132710780</v>
+        <v>132710466</v>
       </c>
       <c r="B30" t="n">
-        <v>57958</v>
+        <v>99195</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3739,10 +3743,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>758184</v>
+        <v>758166</v>
       </c>
       <c r="R30" t="n">
-        <v>7176243</v>
+        <v>7176297</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3777,17 +3781,13 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Tommy Boström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 1095-2026 artfynd.xlsx
+++ b/artfynd/A 1095-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132710617</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132695613</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132710403</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132710416</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132710436</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132695329</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,6 +1434,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132710803</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1500,6 +1540,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132695395</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1610,6 +1655,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132710050</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1715,6 +1765,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132710116</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1829,6 +1884,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132710636</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1943,6 +2003,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132710791</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2053,6 +2118,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132710910</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2158,6 +2228,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132710963</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2268,6 +2343,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132710822</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2378,6 +2458,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132695423</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2487,6 +2572,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132695489</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2597,6 +2687,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132695568</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2707,6 +2802,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132695598</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2817,6 +2917,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132695652</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2927,6 +3032,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132710098</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3037,6 +3147,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132710187</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3147,6 +3262,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132710308</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3257,6 +3377,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132710491</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3367,6 +3492,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132710580</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3477,6 +3607,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132710603</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3587,6 +3722,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132710780</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3697,6 +3837,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132710895</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3803,8 +3948,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132710466</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>